--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/120.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/120.xlsx
@@ -426,13 +426,13 @@
         <v>-18.54186979483897</v>
       </c>
       <c r="E2">
-        <v>-13.61582374573216</v>
+        <v>-14.07749714234015</v>
       </c>
       <c r="F2">
-        <v>-2.221138940906948</v>
+        <v>-2.533099619699033</v>
       </c>
       <c r="G2">
-        <v>-10.666191544372</v>
+        <v>-11.42662716528814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.56210295751526</v>
       </c>
       <c r="E3">
-        <v>-13.72952467111675</v>
+        <v>-15.58964971145544</v>
       </c>
       <c r="F3">
-        <v>-2.207701164898734</v>
+        <v>-2.34171775679325</v>
       </c>
       <c r="G3">
-        <v>-10.91885237992918</v>
+        <v>-11.45713053188698</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.58785473243378</v>
       </c>
       <c r="E4">
-        <v>-13.40841057923285</v>
+        <v>-15.08025072728062</v>
       </c>
       <c r="F4">
-        <v>-2.157260217007467</v>
+        <v>-2.35821717872221</v>
       </c>
       <c r="G4">
-        <v>-9.744111916409878</v>
+        <v>-11.51812402290251</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.58771130019737</v>
       </c>
       <c r="E5">
-        <v>-15.89825162965616</v>
+        <v>-15.7970266501627</v>
       </c>
       <c r="F5">
-        <v>-2.463802544617841</v>
+        <v>-1.857651324558525</v>
       </c>
       <c r="G5">
-        <v>-9.698843516705885</v>
+        <v>-11.22047618401218</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.51857259398669</v>
       </c>
       <c r="E6">
-        <v>-15.76274157345063</v>
+        <v>-17.07320949568631</v>
       </c>
       <c r="F6">
-        <v>-2.553869275589426</v>
+        <v>-1.940917159153126</v>
       </c>
       <c r="G6">
-        <v>-9.126506472240063</v>
+        <v>-10.77128812306171</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.36648476946277</v>
       </c>
       <c r="E7">
-        <v>-15.46652050318689</v>
+        <v>-16.95342230123541</v>
       </c>
       <c r="F7">
-        <v>-1.859029727916783</v>
+        <v>-2.22494777422502</v>
       </c>
       <c r="G7">
-        <v>-9.879754898790438</v>
+        <v>-11.05357172010428</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.11816158334065</v>
       </c>
       <c r="E8">
-        <v>-16.62696461002245</v>
+        <v>-17.0355416488905</v>
       </c>
       <c r="F8">
-        <v>-2.336750865846064</v>
+        <v>-2.139608536021212</v>
       </c>
       <c r="G8">
-        <v>-10.82806397906021</v>
+        <v>-10.36792794401137</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.74536957733746</v>
       </c>
       <c r="E9">
-        <v>-17.7576973988937</v>
+        <v>-18.58823764579647</v>
       </c>
       <c r="F9">
-        <v>-1.930092882300745</v>
+        <v>-1.807885496100539</v>
       </c>
       <c r="G9">
-        <v>-8.587857539181867</v>
+        <v>-10.02124430459335</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.2383481052105</v>
       </c>
       <c r="E10">
-        <v>-19.47952284303814</v>
+        <v>-17.98906619289359</v>
       </c>
       <c r="F10">
-        <v>-2.295864307578686</v>
+        <v>-1.632741291024431</v>
       </c>
       <c r="G10">
-        <v>-8.1945183814789</v>
+        <v>-10.30143563685511</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.6097561463511</v>
       </c>
       <c r="E11">
-        <v>-18.77367412793657</v>
+        <v>-19.35479961191888</v>
       </c>
       <c r="F11">
-        <v>-1.746819079533563</v>
+        <v>-1.451747983717156</v>
       </c>
       <c r="G11">
-        <v>-8.631126369380141</v>
+        <v>-10.34789914349878</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.86278235222166</v>
       </c>
       <c r="E12">
-        <v>-17.90466449433863</v>
+        <v>-19.29746913098177</v>
       </c>
       <c r="F12">
-        <v>-2.119307736080805</v>
+        <v>-1.546137135796549</v>
       </c>
       <c r="G12">
-        <v>-8.663602821120392</v>
+        <v>-9.457276319250806</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.00173596575964</v>
       </c>
       <c r="E13">
-        <v>-19.15767060989098</v>
+        <v>-20.88724427306254</v>
       </c>
       <c r="F13">
-        <v>-1.721677300491195</v>
+        <v>-1.347994966516518</v>
       </c>
       <c r="G13">
-        <v>-8.511003224487686</v>
+        <v>-9.338914384585243</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.07269808678277</v>
       </c>
       <c r="E14">
-        <v>-20.02369597911786</v>
+        <v>-20.72293765064224</v>
       </c>
       <c r="F14">
-        <v>-1.543328141933656</v>
+        <v>-1.366297744281373</v>
       </c>
       <c r="G14">
-        <v>-7.364601030784545</v>
+        <v>-7.937179745074733</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.10690868504236</v>
       </c>
       <c r="E15">
-        <v>-19.76488463263148</v>
+        <v>-21.79069747996282</v>
       </c>
       <c r="F15">
-        <v>-0.8515808897756639</v>
+        <v>-1.117830598546467</v>
       </c>
       <c r="G15">
-        <v>-7.892119909739713</v>
+        <v>-8.12043168285555</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.12817793875973</v>
       </c>
       <c r="E16">
-        <v>-21.15287550140447</v>
+        <v>-22.13014736310378</v>
       </c>
       <c r="F16">
-        <v>-0.9941495467366812</v>
+        <v>-0.9206004617769187</v>
       </c>
       <c r="G16">
-        <v>-6.306232864061704</v>
+        <v>-7.425200566880904</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.19298159559736</v>
       </c>
       <c r="E17">
-        <v>-22.46589295450647</v>
+        <v>-23.5606651312828</v>
       </c>
       <c r="F17">
-        <v>-0.2011981638764657</v>
+        <v>-0.8407160229205456</v>
       </c>
       <c r="G17">
-        <v>-5.666777819332699</v>
+        <v>-7.219566030709075</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.34394378913521</v>
       </c>
       <c r="E18">
-        <v>-25.48777535914295</v>
+        <v>-23.55941527245668</v>
       </c>
       <c r="F18">
-        <v>-0.6605005526044991</v>
+        <v>-0.6323335758071076</v>
       </c>
       <c r="G18">
-        <v>-6.708834928183552</v>
+        <v>-7.061745703760939</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.601074989141233</v>
       </c>
       <c r="E19">
-        <v>-24.35851885279821</v>
+        <v>-24.31686142040165</v>
       </c>
       <c r="F19">
-        <v>-0.4961681988697304</v>
+        <v>-0.4172073896674788</v>
       </c>
       <c r="G19">
-        <v>-6.154917759098236</v>
+        <v>-6.63639357069322</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.999404600432033</v>
       </c>
       <c r="E20">
-        <v>-23.27555240775987</v>
+        <v>-25.36033051514508</v>
       </c>
       <c r="F20">
-        <v>-0.8960832717562618</v>
+        <v>-0.1422101211231129</v>
       </c>
       <c r="G20">
-        <v>-5.641316413590165</v>
+        <v>-6.942238320338788</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.562606983408763</v>
       </c>
       <c r="E21">
-        <v>-26.14084470968512</v>
+        <v>-25.86896871568662</v>
       </c>
       <c r="F21">
-        <v>-0.5222468614446645</v>
+        <v>0.2069939560988383</v>
       </c>
       <c r="G21">
-        <v>-6.631480721112941</v>
+        <v>-6.51193030059878</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.285817840647251</v>
       </c>
       <c r="E22">
-        <v>-25.28873534108381</v>
+        <v>-27.07389602269953</v>
       </c>
       <c r="F22">
-        <v>-0.4941676915919696</v>
+        <v>0.2542813092876481</v>
       </c>
       <c r="G22">
-        <v>-5.632414356635064</v>
+        <v>-6.336398555015543</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.161647949026333</v>
       </c>
       <c r="E23">
-        <v>-26.79522278921552</v>
+        <v>-26.84508581651397</v>
       </c>
       <c r="F23">
-        <v>-0.04287395891420177</v>
+        <v>0.488614850395989</v>
       </c>
       <c r="G23">
-        <v>-5.556715422334089</v>
+        <v>-7.289709869595153</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.188795304394425</v>
       </c>
       <c r="E24">
-        <v>-27.12922038965124</v>
+        <v>-27.96534877347948</v>
       </c>
       <c r="F24">
-        <v>0.6273191734229466</v>
+        <v>0.4374871859278007</v>
       </c>
       <c r="G24">
-        <v>-4.903395812886617</v>
+        <v>-6.372711929035809</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.339471506770883</v>
       </c>
       <c r="E25">
-        <v>-28.21572357288957</v>
+        <v>-28.10309136737079</v>
       </c>
       <c r="F25">
-        <v>-0.1168032645118492</v>
+        <v>0.4431407934519074</v>
       </c>
       <c r="G25">
-        <v>-5.666215026591023</v>
+        <v>-6.84406740291724</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.573234625604529</v>
       </c>
       <c r="E26">
-        <v>-26.9589271245928</v>
+        <v>-28.39751463345349</v>
       </c>
       <c r="F26">
-        <v>0.5855727697914628</v>
+        <v>0.5465036496058269</v>
       </c>
       <c r="G26">
-        <v>-5.695043257146997</v>
+        <v>-6.170152889669962</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.87224289560781</v>
       </c>
       <c r="E27">
-        <v>-27.9409176562081</v>
+        <v>-29.33646201962588</v>
       </c>
       <c r="F27">
-        <v>0.5542049813496539</v>
+        <v>0.5922883443259583</v>
       </c>
       <c r="G27">
-        <v>-6.151064284090524</v>
+        <v>-6.389658611651338</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.200655932095639</v>
       </c>
       <c r="E28">
-        <v>-27.94199543302192</v>
+        <v>-28.86843064551113</v>
       </c>
       <c r="F28">
-        <v>0.6331160885077376</v>
+        <v>0.2704659516035448</v>
       </c>
       <c r="G28">
-        <v>-5.483055784085305</v>
+        <v>-6.80968407694637</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.514887273247862</v>
       </c>
       <c r="E29">
-        <v>-28.66785547476339</v>
+        <v>-28.97286631307602</v>
       </c>
       <c r="F29">
-        <v>0.02737076847579351</v>
+        <v>0.682673168380218</v>
       </c>
       <c r="G29">
-        <v>-6.310016817613091</v>
+        <v>-6.713327338480343</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.80055458766417</v>
       </c>
       <c r="E30">
-        <v>-28.49880754005705</v>
+        <v>-28.98543735692131</v>
       </c>
       <c r="F30">
-        <v>0.6219223597937079</v>
+        <v>0.5457937387416277</v>
       </c>
       <c r="G30">
-        <v>-5.088296402345991</v>
+        <v>-6.74613484477452</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.04170444755927</v>
       </c>
       <c r="E31">
-        <v>-27.411874151788</v>
+        <v>-29.57082639918185</v>
       </c>
       <c r="F31">
-        <v>0.1162943524315148</v>
+        <v>0.5812934237886005</v>
       </c>
       <c r="G31">
-        <v>-5.896188693567574</v>
+        <v>-6.957413861090807</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.21717178074798</v>
       </c>
       <c r="E32">
-        <v>-27.41056995127379</v>
+        <v>-28.79257417740864</v>
       </c>
       <c r="F32">
-        <v>0.5756489283059247</v>
+        <v>0.6271410744313447</v>
       </c>
       <c r="G32">
-        <v>-5.495000232390996</v>
+        <v>-6.689564242599454</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.33132353494629</v>
       </c>
       <c r="E33">
-        <v>-27.63471582923145</v>
+        <v>-28.75000199326253</v>
       </c>
       <c r="F33">
-        <v>0.113979893908093</v>
+        <v>0.3541807613304629</v>
       </c>
       <c r="G33">
-        <v>-5.588102704591919</v>
+        <v>-6.187880861032759</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.39527495146633</v>
       </c>
       <c r="E34">
-        <v>-26.63862815803027</v>
+        <v>-28.53202389690332</v>
       </c>
       <c r="F34">
-        <v>0.1785900662242461</v>
+        <v>0.5111265629344683</v>
       </c>
       <c r="G34">
-        <v>-5.188867465283511</v>
+        <v>-6.694503576544046</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.41312099465881</v>
       </c>
       <c r="E35">
-        <v>-27.32016349618466</v>
+        <v>-28.55928531042949</v>
       </c>
       <c r="F35">
-        <v>0.2008209622131764</v>
+        <v>0.3329770409210039</v>
       </c>
       <c r="G35">
-        <v>-6.324805024537016</v>
+        <v>-6.905054272841694</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.39713935912214</v>
       </c>
       <c r="E36">
-        <v>-25.61551908242532</v>
+        <v>-28.06660092381698</v>
       </c>
       <c r="F36">
-        <v>0.09540044143070291</v>
+        <v>0.1916004046526151</v>
       </c>
       <c r="G36">
-        <v>-6.050129061143685</v>
+        <v>-6.615067036329235</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.37365394966677</v>
       </c>
       <c r="E37">
-        <v>-26.68165771805116</v>
+        <v>-27.6048097868848</v>
       </c>
       <c r="F37">
-        <v>-0.1563909426916376</v>
+        <v>0.3477973621244899</v>
       </c>
       <c r="G37">
-        <v>-6.343671823565322</v>
+        <v>-7.034751515433721</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.35584991775311</v>
       </c>
       <c r="E38">
-        <v>-24.68568298595636</v>
+        <v>-27.2009287755627</v>
       </c>
       <c r="F38">
-        <v>0.5325266064183908</v>
+        <v>0.4015194732982462</v>
       </c>
       <c r="G38">
-        <v>-6.098853670390678</v>
+        <v>-6.548819709542879</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.34800266720801</v>
       </c>
       <c r="E39">
-        <v>-25.81335452639842</v>
+        <v>-26.46645557625865</v>
       </c>
       <c r="F39">
-        <v>0.6179776742215767</v>
+        <v>0.3413211857694033</v>
       </c>
       <c r="G39">
-        <v>-5.567448210972406</v>
+        <v>-6.259852121056515</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.37385261953352</v>
       </c>
       <c r="E40">
-        <v>-25.15102897498457</v>
+        <v>-26.73861686411963</v>
       </c>
       <c r="F40">
-        <v>0.1097403095405652</v>
+        <v>0.3821066832136398</v>
       </c>
       <c r="G40">
-        <v>-5.401755406731883</v>
+        <v>-6.676060527344767</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.43968335439054</v>
       </c>
       <c r="E41">
-        <v>-24.23961471077881</v>
+        <v>-26.2815806248955</v>
       </c>
       <c r="F41">
-        <v>0.1403882467093413</v>
+        <v>0.1962757102740155</v>
       </c>
       <c r="G41">
-        <v>-5.049079679887785</v>
+        <v>-6.376605130589992</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.53356932236833</v>
       </c>
       <c r="E42">
-        <v>-24.66363837448702</v>
+        <v>-26.24856352090558</v>
       </c>
       <c r="F42">
-        <v>0.01265564993246309</v>
+        <v>-0.01396559329130462</v>
       </c>
       <c r="G42">
-        <v>-5.64110784922119</v>
+        <v>-6.625068194403373</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.66510564733175</v>
       </c>
       <c r="E43">
-        <v>-24.29988417134689</v>
+        <v>-26.63698432196549</v>
       </c>
       <c r="F43">
-        <v>0.5021859935560533</v>
+        <v>0.2269584388737092</v>
       </c>
       <c r="G43">
-        <v>-5.232361412578456</v>
+        <v>-5.84733497304455</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.83226114036784</v>
       </c>
       <c r="E44">
-        <v>-23.32108168543299</v>
+        <v>-23.31793439599766</v>
       </c>
       <c r="F44">
-        <v>0.01660944754602513</v>
+        <v>0.03153497140966663</v>
       </c>
       <c r="G44">
-        <v>-6.366673493972178</v>
+        <v>-6.50638844736604</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.01458934344295</v>
       </c>
       <c r="E45">
-        <v>-23.3035519625493</v>
+        <v>-23.76710014739646</v>
       </c>
       <c r="F45">
-        <v>0.2129747687470507</v>
+        <v>0.2630305257960165</v>
       </c>
       <c r="G45">
-        <v>-5.533349591917913</v>
+        <v>-6.528095694467041</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.20848153729326</v>
       </c>
       <c r="E46">
-        <v>-22.93012041045478</v>
+        <v>-24.15370050190529</v>
       </c>
       <c r="F46">
-        <v>0.3360072088804445</v>
+        <v>0.4464426659194662</v>
       </c>
       <c r="G46">
-        <v>-5.849639112739882</v>
+        <v>-6.168017587797132</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.41131973107991</v>
       </c>
       <c r="E47">
-        <v>-22.35556121378359</v>
+        <v>-23.18484254491223</v>
       </c>
       <c r="F47">
-        <v>0.1737449452852718</v>
+        <v>0.6337034009963224</v>
       </c>
       <c r="G47">
-        <v>-5.858137283139191</v>
+        <v>-6.595220315821304</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.60571333708323</v>
       </c>
       <c r="E48">
-        <v>-21.57657311498413</v>
+        <v>-22.30503702928001</v>
       </c>
       <c r="F48">
-        <v>0.2580255299483019</v>
+        <v>0.1430522762767445</v>
       </c>
       <c r="G48">
-        <v>-5.019089447847527</v>
+        <v>-6.751362196181029</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.77890315448148</v>
       </c>
       <c r="E49">
-        <v>-20.7193692131242</v>
+        <v>-22.66731494989364</v>
       </c>
       <c r="F49">
-        <v>0.3790624330083516</v>
+        <v>0.2977954489567061</v>
       </c>
       <c r="G49">
-        <v>-5.655356437222213</v>
+        <v>-6.603086172022612</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.93492040064311</v>
       </c>
       <c r="E50">
-        <v>-20.7038456042259</v>
+        <v>-22.00379388134176</v>
       </c>
       <c r="F50">
-        <v>-0.3451112611322266</v>
+        <v>0.2437817524571644</v>
       </c>
       <c r="G50">
-        <v>-6.009151128458586</v>
+        <v>-6.586129557770465</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.06392005363151</v>
       </c>
       <c r="E51">
-        <v>-20.24605310984249</v>
+        <v>-21.09815342149578</v>
       </c>
       <c r="F51">
-        <v>0.2997396272510766</v>
+        <v>0.2159105028225722</v>
       </c>
       <c r="G51">
-        <v>-4.994045170842941</v>
+        <v>-6.490497828777539</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.14972510112854</v>
       </c>
       <c r="E52">
-        <v>-19.32602115960013</v>
+        <v>-21.19122261930142</v>
       </c>
       <c r="F52">
-        <v>0.08350591389390481</v>
+        <v>-0.1527527530585422</v>
       </c>
       <c r="G52">
-        <v>-6.906537397243287</v>
+        <v>-6.954050346822908</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.20190899371485</v>
       </c>
       <c r="E53">
-        <v>-19.93767308686815</v>
+        <v>-20.43621731884659</v>
       </c>
       <c r="F53">
-        <v>0.1860404026450248</v>
+        <v>0.3000635189055711</v>
       </c>
       <c r="G53">
-        <v>-5.797855559414603</v>
+        <v>-7.271117845846605</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.21760496488814</v>
       </c>
       <c r="E54">
-        <v>-19.1354856157274</v>
+        <v>-19.84025202554114</v>
       </c>
       <c r="F54">
-        <v>-0.1215481529950848</v>
+        <v>0.22357952823769</v>
       </c>
       <c r="G54">
-        <v>-6.8955794915083</v>
+        <v>-7.751511109050248</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.1819752032907</v>
       </c>
       <c r="E55">
-        <v>-18.89056762749656</v>
+        <v>-19.85287741107453</v>
       </c>
       <c r="F55">
-        <v>0.1635957878661722</v>
+        <v>0.197860377115571</v>
       </c>
       <c r="G55">
-        <v>-7.621542401724</v>
+        <v>-7.291428042730034</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.10560868990365</v>
       </c>
       <c r="E56">
-        <v>-17.86880350867189</v>
+        <v>-19.5961038778916</v>
       </c>
       <c r="F56">
-        <v>-0.3738249604154659</v>
+        <v>0.3810720523275432</v>
       </c>
       <c r="G56">
-        <v>-5.837181529875605</v>
+        <v>-7.24188903928038</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.99292003250868</v>
       </c>
       <c r="E57">
-        <v>-17.83174247739311</v>
+        <v>-19.15964502455832</v>
       </c>
       <c r="F57">
-        <v>-0.2007301362938839</v>
+        <v>0.01845090828244843</v>
       </c>
       <c r="G57">
-        <v>-6.584341863179259</v>
+        <v>-7.46587392937639</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.83563874864004</v>
       </c>
       <c r="E58">
-        <v>-17.80697625304516</v>
+        <v>-18.08631517220831</v>
       </c>
       <c r="F58">
-        <v>0.586600773738337</v>
+        <v>0.188704432212428</v>
       </c>
       <c r="G58">
-        <v>-6.518273305852023</v>
+        <v>-7.448261827107467</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.64136985061043</v>
       </c>
       <c r="E59">
-        <v>-17.26146268865917</v>
+        <v>-18.54673418151617</v>
       </c>
       <c r="F59">
-        <v>-0.06062918582580637</v>
+        <v>0.2767557452930015</v>
       </c>
       <c r="G59">
-        <v>-6.452956242362203</v>
+        <v>-7.385745485143871</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.4222252352047</v>
       </c>
       <c r="E60">
-        <v>-15.8817453418982</v>
+        <v>-17.53615086501644</v>
       </c>
       <c r="F60">
-        <v>-0.2363491062468599</v>
+        <v>-0.05003933694841749</v>
       </c>
       <c r="G60">
-        <v>-6.656038347923254</v>
+        <v>-6.71420132250271</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.17724215813639</v>
       </c>
       <c r="E61">
-        <v>-16.68111157373217</v>
+        <v>-17.34757615038903</v>
       </c>
       <c r="F61">
-        <v>0.3404398028528247</v>
+        <v>-0.1767165936541291</v>
       </c>
       <c r="G61">
-        <v>-6.891437999038672</v>
+        <v>-7.175499359035836</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.9068788952428</v>
       </c>
       <c r="E62">
-        <v>-15.15662796989399</v>
+        <v>-16.97884968278848</v>
       </c>
       <c r="F62">
-        <v>0.04562384419648062</v>
+        <v>-0.1953349793994508</v>
       </c>
       <c r="G62">
-        <v>-7.539583225808263</v>
+        <v>-7.621986014826263</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.62896108623768</v>
       </c>
       <c r="E63">
-        <v>-16.09070724650814</v>
+        <v>-17.32641006287718</v>
       </c>
       <c r="F63">
-        <v>-0.3161946118353015</v>
+        <v>-0.03866088230356348</v>
       </c>
       <c r="G63">
-        <v>-7.32964829098092</v>
+        <v>-8.010607645135767</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.34652236109053</v>
       </c>
       <c r="E64">
-        <v>-15.90818710162898</v>
+        <v>-16.59585852206377</v>
       </c>
       <c r="F64">
-        <v>-0.5813251962449224</v>
+        <v>-0.1070972836532474</v>
       </c>
       <c r="G64">
-        <v>-7.090600418681226</v>
+        <v>-7.66737359416967</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.05453734359081</v>
       </c>
       <c r="E65">
-        <v>-15.90962715636342</v>
+        <v>-16.4931527315698</v>
       </c>
       <c r="F65">
-        <v>0.0743002669465939</v>
+        <v>-0.3873447447965566</v>
       </c>
       <c r="G65">
-        <v>-6.169742382023093</v>
+        <v>-7.855710529898809</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.770830774425386</v>
       </c>
       <c r="E66">
-        <v>-14.91406025967313</v>
+        <v>-15.90511226777778</v>
       </c>
       <c r="F66">
-        <v>-0.1679243020408151</v>
+        <v>-0.07779378677921492</v>
       </c>
       <c r="G66">
-        <v>-7.536865267920522</v>
+        <v>-7.578472204258082</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.499799214017026</v>
       </c>
       <c r="E67">
-        <v>-14.62149819640758</v>
+        <v>-16.02846337127271</v>
       </c>
       <c r="F67">
-        <v>-0.225684704303219</v>
+        <v>-0.06531443185604037</v>
       </c>
       <c r="G67">
-        <v>-7.016656073516065</v>
+        <v>-8.170977092149142</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.232922606255967</v>
       </c>
       <c r="E68">
-        <v>-15.5777579387113</v>
+        <v>-16.57135494920826</v>
       </c>
       <c r="F68">
-        <v>-0.9095666079716294</v>
+        <v>-0.1339512981172018</v>
       </c>
       <c r="G68">
-        <v>-7.086531758213462</v>
+        <v>-7.689196710364546</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.981935553052024</v>
       </c>
       <c r="E69">
-        <v>-15.67300986098864</v>
+        <v>-15.73820630127707</v>
       </c>
       <c r="F69">
-        <v>-0.2582453418050592</v>
+        <v>-0.1194482416289881</v>
       </c>
       <c r="G69">
-        <v>-6.184550452220252</v>
+        <v>-7.847914195153825</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.751848002400077</v>
       </c>
       <c r="E70">
-        <v>-14.46243554688816</v>
+        <v>-15.28499209411541</v>
       </c>
       <c r="F70">
-        <v>-0.4786705942203965</v>
+        <v>-0.2439974224769077</v>
       </c>
       <c r="G70">
-        <v>-7.04012122029842</v>
+        <v>-8.108864636741336</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.534646685038833</v>
       </c>
       <c r="E71">
-        <v>-14.11158296619589</v>
+        <v>-16.71133460925936</v>
       </c>
       <c r="F71">
-        <v>-0.1131857840638238</v>
+        <v>-0.6010030638984246</v>
       </c>
       <c r="G71">
-        <v>-7.126725091605754</v>
+        <v>-8.35086220511652</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.33346267540359</v>
       </c>
       <c r="E72">
-        <v>-13.34197786554032</v>
+        <v>-16.35427349070257</v>
       </c>
       <c r="F72">
-        <v>-0.4518588264939849</v>
+        <v>-0.07594818420577762</v>
       </c>
       <c r="G72">
-        <v>-7.508285328279993</v>
+        <v>-8.308318384391347</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.156001319091281</v>
       </c>
       <c r="E73">
-        <v>-15.35030174625403</v>
+        <v>-16.42737211813438</v>
       </c>
       <c r="F73">
-        <v>-0.373969096343553</v>
+        <v>-0.3415575649742167</v>
       </c>
       <c r="G73">
-        <v>-6.73882516022381</v>
+        <v>-7.60650921443017</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.997489363751408</v>
       </c>
       <c r="E74">
-        <v>-16.25891288504905</v>
+        <v>-15.95735274393026</v>
       </c>
       <c r="F74">
-        <v>-0.8071580310657348</v>
+        <v>-0.4058537860447087</v>
       </c>
       <c r="G74">
-        <v>-7.534862387869262</v>
+        <v>-7.878599641757329</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.852925427564592</v>
       </c>
       <c r="E75">
-        <v>-17.13551676955784</v>
+        <v>-16.28095296804438</v>
       </c>
       <c r="F75">
-        <v>-0.6274520067024101</v>
+        <v>-0.7432345753265026</v>
       </c>
       <c r="G75">
-        <v>-6.966547656233656</v>
+        <v>-7.645576962339109</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.733227660471107</v>
       </c>
       <c r="E76">
-        <v>-15.76693041190772</v>
+        <v>-16.55917788260164</v>
       </c>
       <c r="F76">
-        <v>-0.7102531271840402</v>
+        <v>-0.6846052156585619</v>
       </c>
       <c r="G76">
-        <v>-6.519905404802884</v>
+        <v>-7.938494031653823</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.635909859242755</v>
       </c>
       <c r="E77">
-        <v>-15.12419051057705</v>
+        <v>-16.78080140053702</v>
       </c>
       <c r="F77">
-        <v>-1.00728414027547</v>
+        <v>-0.7248945210285215</v>
       </c>
       <c r="G77">
-        <v>-5.256806480840434</v>
+        <v>-7.362710709281622</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.551452354356204</v>
       </c>
       <c r="E78">
-        <v>-16.60640533802763</v>
+        <v>-17.48427719525857</v>
       </c>
       <c r="F78">
-        <v>-1.577512379544983</v>
+        <v>-0.8685259733673306</v>
       </c>
       <c r="G78">
-        <v>-6.897161932276072</v>
+        <v>-7.582951372372716</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.490998023855102</v>
       </c>
       <c r="E79">
-        <v>-16.29646751999466</v>
+        <v>-17.72046428560263</v>
       </c>
       <c r="F79">
-        <v>-0.5689535290841118</v>
+        <v>-0.873775337598871</v>
       </c>
       <c r="G79">
-        <v>-6.310361114349175</v>
+        <v>-7.604274596191162</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.456344717025214</v>
       </c>
       <c r="E80">
-        <v>-16.88482044849321</v>
+        <v>-18.28557255701982</v>
       </c>
       <c r="F80">
-        <v>-1.298356706638563</v>
+        <v>-1.024656661446981</v>
       </c>
       <c r="G80">
-        <v>-6.365905447407068</v>
+        <v>-6.72074627103385</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.437709651373123</v>
       </c>
       <c r="E81">
-        <v>-16.7618361513929</v>
+        <v>-18.87550139447304</v>
       </c>
       <c r="F81">
-        <v>-1.597166224543804</v>
+        <v>-0.8490916457302514</v>
       </c>
       <c r="G81">
-        <v>-6.16248235565547</v>
+        <v>-6.411849198401073</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.444740914245843</v>
       </c>
       <c r="E82">
-        <v>-18.54588282840273</v>
+        <v>-19.23279346520422</v>
       </c>
       <c r="F82">
-        <v>-1.442319505938492</v>
+        <v>-0.9286248568078376</v>
       </c>
       <c r="G82">
-        <v>-6.296440270356539</v>
+        <v>-7.519299513289148</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.482269533447884</v>
       </c>
       <c r="E83">
-        <v>-19.54737749756907</v>
+        <v>-20.93136066684527</v>
       </c>
       <c r="F83">
-        <v>-1.743830329944262</v>
+        <v>-1.021952041876841</v>
       </c>
       <c r="G83">
-        <v>-5.593339987635047</v>
+        <v>-6.475924807313667</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.543045522728062</v>
       </c>
       <c r="E84">
-        <v>-20.34387267688218</v>
+        <v>-21.1432072093981</v>
       </c>
       <c r="F84">
-        <v>-0.8959407925629802</v>
+        <v>-1.127153045297573</v>
       </c>
       <c r="G84">
-        <v>-5.856309862001514</v>
+        <v>-6.867764287887343</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.629246004514314</v>
       </c>
       <c r="E85">
-        <v>-21.54418999735528</v>
+        <v>-21.92926425612352</v>
       </c>
       <c r="F85">
-        <v>-1.042789623894263</v>
+        <v>-1.22479850963737</v>
       </c>
       <c r="G85">
-        <v>-5.156583025184538</v>
+        <v>-7.037946191879118</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.74829401402271</v>
       </c>
       <c r="E86">
-        <v>-22.25066817034392</v>
+        <v>-22.78630513291919</v>
       </c>
       <c r="F86">
-        <v>-1.493114166710755</v>
+        <v>-1.381719460219291</v>
       </c>
       <c r="G86">
-        <v>-6.494953823073398</v>
+        <v>-7.141831110901448</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.895536986707871</v>
       </c>
       <c r="E87">
-        <v>-22.50344306097807</v>
+        <v>-24.28249483115744</v>
       </c>
       <c r="F87">
-        <v>-1.840885168325863</v>
+        <v>-1.144152801137824</v>
       </c>
       <c r="G87">
-        <v>-5.916412816266982</v>
+        <v>-7.162406151428018</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.065269840624005</v>
       </c>
       <c r="E88">
-        <v>-23.5570061242846</v>
+        <v>-24.42453494688203</v>
       </c>
       <c r="F88">
-        <v>-1.93468369444706</v>
+        <v>-1.836319207201632</v>
       </c>
       <c r="G88">
-        <v>-4.71300964946867</v>
+        <v>-6.848768377583005</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.268624961530104</v>
       </c>
       <c r="E89">
-        <v>-25.07805714482497</v>
+        <v>-26.28079267041817</v>
       </c>
       <c r="F89">
-        <v>-1.768525618956521</v>
+        <v>-1.987133433290116</v>
       </c>
       <c r="G89">
-        <v>-5.446090232593804</v>
+        <v>-6.92742031850501</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.504325871608426</v>
       </c>
       <c r="E90">
-        <v>-26.79928030192639</v>
+        <v>-27.47020089700679</v>
       </c>
       <c r="F90">
-        <v>-2.200549040742964</v>
+        <v>-1.748039264717886</v>
       </c>
       <c r="G90">
-        <v>-7.361485807432091</v>
+        <v>-7.079473675123736</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.762063528782793</v>
       </c>
       <c r="E91">
-        <v>-29.69388994457729</v>
+        <v>-28.64391343268484</v>
       </c>
       <c r="F91">
-        <v>-2.605528751930211</v>
+        <v>-1.569947728422618</v>
       </c>
       <c r="G91">
-        <v>-6.931273793512722</v>
+        <v>-7.545221084861642</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.053502842775748</v>
       </c>
       <c r="E92">
-        <v>-30.39695364816415</v>
+        <v>-30.47345768804973</v>
       </c>
       <c r="F92">
-        <v>-2.437829913070465</v>
+        <v>-2.03172942078723</v>
       </c>
       <c r="G92">
-        <v>-8.114383316155301</v>
+        <v>-7.990628502806266</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.380547452885647</v>
       </c>
       <c r="E93">
-        <v>-31.9570808709167</v>
+        <v>-32.53576097893487</v>
       </c>
       <c r="F93">
-        <v>-2.282287365846802</v>
+        <v>-1.793280550421781</v>
       </c>
       <c r="G93">
-        <v>-7.411690230535139</v>
+        <v>-7.579551442103885</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.727600421085414</v>
       </c>
       <c r="E94">
-        <v>-34.11172427529225</v>
+        <v>-33.69451370072858</v>
       </c>
       <c r="F94">
-        <v>-2.20989551014875</v>
+        <v>-1.808646765743712</v>
       </c>
       <c r="G94">
-        <v>-7.39937500112905</v>
+        <v>-7.939795076050757</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.09997595021051</v>
       </c>
       <c r="E95">
-        <v>-35.09049959036211</v>
+        <v>-36.01677177778703</v>
       </c>
       <c r="F95">
-        <v>-1.8712257811882</v>
+        <v>-1.965790547156987</v>
       </c>
       <c r="G95">
-        <v>-7.404297782345946</v>
+        <v>-7.379673944624847</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.49703696079414</v>
       </c>
       <c r="E96">
-        <v>-36.67199894619386</v>
+        <v>-38.43519426463537</v>
       </c>
       <c r="F96">
-        <v>-2.46461600140739</v>
+        <v>-2.174342809587999</v>
       </c>
       <c r="G96">
-        <v>-7.207171348210044</v>
+        <v>-8.350133885097881</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.89724155816241</v>
       </c>
       <c r="E97">
-        <v>-37.71332607273167</v>
+        <v>-39.6053564766914</v>
       </c>
       <c r="F97">
-        <v>-2.579710196719756</v>
+        <v>-1.933078318420434</v>
       </c>
       <c r="G97">
-        <v>-7.954606456793456</v>
+        <v>-7.912251337164021</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.29479600301218</v>
       </c>
       <c r="E98">
-        <v>-41.15630901110441</v>
+        <v>-41.89543974592536</v>
       </c>
       <c r="F98">
-        <v>-2.444488330254168</v>
+        <v>-2.123024620617166</v>
       </c>
       <c r="G98">
-        <v>-7.244285874250813</v>
+        <v>-8.535613820026628</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.67667999610799</v>
       </c>
       <c r="E99">
-        <v>-43.04339205721077</v>
+        <v>-44.35455736444362</v>
       </c>
       <c r="F99">
-        <v>-3.057007210538803</v>
+        <v>-2.169438046196023</v>
       </c>
       <c r="G99">
-        <v>-8.370877763446954</v>
+        <v>-9.156033227904823</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.0358041824368</v>
       </c>
       <c r="E100">
-        <v>-45.47532977473499</v>
+        <v>-46.20440956149591</v>
       </c>
       <c r="F100">
-        <v>-2.475491637038745</v>
+        <v>-2.421838280359421</v>
       </c>
       <c r="G100">
-        <v>-8.208267077103493</v>
+        <v>-8.572725035521858</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.33137535909123</v>
       </c>
       <c r="E101">
-        <v>-48.28300403762365</v>
+        <v>-48.1210341077913</v>
       </c>
       <c r="F101">
-        <v>-2.633985657318583</v>
+        <v>-2.319561413870571</v>
       </c>
       <c r="G101">
-        <v>-7.623356580679521</v>
+        <v>-9.322984039450269</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.59773019689718</v>
       </c>
       <c r="E102">
-        <v>-49.73144663804353</v>
+        <v>-50.54779804376177</v>
       </c>
       <c r="F102">
-        <v>-2.65516535507336</v>
+        <v>-2.567670704887468</v>
       </c>
       <c r="G102">
-        <v>-7.924142816741083</v>
+        <v>-8.769083423092651</v>
       </c>
     </row>
   </sheetData>
